--- a/data/trans_camb/P45C_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,43</t>
+          <t>-2,4; 5,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -4,84</t>
+          <t>-11,98; -5,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 10,97</t>
+          <t>0,62; 10,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,52</t>
+          <t>0,6; 7,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,05</t>
+          <t>-5,08; 0,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,86</t>
+          <t>4,5; 10,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 5,24</t>
+          <t>0,23; 5,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -2,85</t>
+          <t>-7,18; -2,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,33</t>
+          <t>3,21; 9,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 37,11</t>
+          <t>-12,9; 36,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,52; -32,09</t>
+          <t>-64,99; -33,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 71,79</t>
+          <t>2,24; 71,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 98,49</t>
+          <t>3,04; 95,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,62; 14,35</t>
+          <t>-44,09; 12,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,72; 139,91</t>
+          <t>39,85; 138,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 44,35</t>
+          <t>1,67; 45,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,7; -24,69</t>
+          <t>-51,33; -21,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,73; 78,12</t>
+          <t>22,66; 77,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,57</t>
+          <t>-3,8; 2,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -0,18</t>
+          <t>-6,83; -0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -0,81</t>
+          <t>-11,49; -0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,25</t>
+          <t>-1,73; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,57</t>
+          <t>-2,26; 3,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 6,12</t>
+          <t>0,29; 6,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,56</t>
+          <t>-2,24; 2,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,65</t>
+          <t>-3,79; 0,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,44</t>
+          <t>-5,48; 1,63</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 16,79</t>
+          <t>-21,13; 20,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,52; -1,09</t>
+          <t>-38,29; -1,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,51; -5,54</t>
+          <t>-62,75; -4,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 41,5</t>
+          <t>-13,0; 42,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 34,41</t>
+          <t>-17,5; 35,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 59,67</t>
+          <t>1,54; 62,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 19,52</t>
+          <t>-14,52; 18,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 5,51</t>
+          <t>-25,0; 5,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 10,56</t>
+          <t>-37,27; 11,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 7,49</t>
+          <t>-0,8; 7,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 5,04</t>
+          <t>-3,17; 4,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 7,82</t>
+          <t>-0,68; 8,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,5</t>
+          <t>-3,88; 3,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 7,5</t>
+          <t>-0,76; 7,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -0,44</t>
+          <t>-11,33; -0,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,2</t>
+          <t>-1,17; 4,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,95</t>
+          <t>-0,34; 5,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 2,3</t>
+          <t>-5,64; 2,37</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 58,61</t>
+          <t>-4,73; 58,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 40,31</t>
+          <t>-19,91; 39,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 59,46</t>
+          <t>-4,68; 65,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 28,56</t>
+          <t>-23,87; 25,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 61,58</t>
+          <t>-4,04; 60,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,0; -3,55</t>
+          <t>-70,46; -2,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 31,79</t>
+          <t>-7,37; 33,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 37,69</t>
+          <t>-2,38; 38,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 16,09</t>
+          <t>-37,18; 17,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,35</t>
+          <t>0,46; 7,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,85</t>
+          <t>-2,08; 4,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,42</t>
+          <t>-4,17; 2,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,52</t>
+          <t>-2,92; 2,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,79</t>
+          <t>-1,47; 4,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,52; -1,4</t>
+          <t>-7,59; -1,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,75</t>
+          <t>-0,73; 3,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,79</t>
+          <t>-0,93; 3,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,78</t>
+          <t>-5,32; -0,61</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 54,49</t>
+          <t>2,73; 52,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 36,7</t>
+          <t>-12,72; 33,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 18,08</t>
+          <t>-25,31; 18,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 20,36</t>
+          <t>-19,45; 21,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 38,62</t>
+          <t>-9,61; 34,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,62; -11,67</t>
+          <t>-49,36; -13,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 28,29</t>
+          <t>-4,42; 28,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 28,61</t>
+          <t>-6,02; 27,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,66; -5,97</t>
+          <t>-34,84; -4,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,82</t>
+          <t>0,05; 3,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,44</t>
+          <t>-4,13; -0,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,07</t>
+          <t>-3,68; 2,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,72</t>
+          <t>-0,62; 2,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,78</t>
+          <t>-0,57; 2,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,59</t>
+          <t>-2,82; 1,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,66</t>
+          <t>0,3; 2,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,76</t>
+          <t>-1,69; 0,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,24</t>
+          <t>-2,23; 1,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,47; 25,95</t>
+          <t>0,36; 23,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -2,96</t>
+          <t>-24,68; -3,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 13,83</t>
+          <t>-22,86; 13,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 23,21</t>
+          <t>-4,9; 22,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 23,87</t>
+          <t>-4,8; 22,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 13,29</t>
+          <t>-21,58; 14,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,31; 19,87</t>
+          <t>2,17; 20,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 5,63</t>
+          <t>-11,48; 5,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 9,04</t>
+          <t>-15,6; 9,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>7,22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,32</t>
+          <t>6,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,23</t>
+          <t>-2,98; 5,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,98; -5,01</t>
+          <t>-11,92; -4,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 10,82</t>
+          <t>0,92; 10,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 7,51</t>
+          <t>0,88; 7,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,97</t>
+          <t>-4,81; 1,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,79</t>
+          <t>4,05; 10,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,35</t>
+          <t>0,18; 5,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -2,57</t>
+          <t>-7,29; -2,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,18</t>
+          <t>3,08; 8,97</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 36,78</t>
+          <t>-16,11; 38,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,99; -33,24</t>
+          <t>-63,89; -31,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 71,45</t>
+          <t>4,83; 72,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 95,35</t>
+          <t>8,28; 96,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 12,03</t>
+          <t>-44,36; 14,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,85; 138,93</t>
+          <t>34,86; 134,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 45,12</t>
+          <t>1,35; 46,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -21,66</t>
+          <t>-51,55; -24,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,66; 77,66</t>
+          <t>22,03; 76,04</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,91</t>
+          <t>-4,22; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,24</t>
+          <t>-7,35; -0,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -0,64</t>
+          <t>-5,23; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,21</t>
+          <t>-1,54; 4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,5</t>
+          <t>-2,23; 3,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,29</t>
+          <t>0,18; 5,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,42</t>
+          <t>-1,89; 2,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,69</t>
+          <t>-3,68; 0,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,63</t>
+          <t>-1,65; 2,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-30,78%</t>
+          <t>-9,03%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,93%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 20,58</t>
+          <t>-22,74; 17,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,29; -1,9</t>
+          <t>-39,92; -2,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,75; -4,12</t>
+          <t>-28,63; 13,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 42,98</t>
+          <t>-12,32; 40,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 35,03</t>
+          <t>-17,85; 33,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 62,02</t>
+          <t>1,13; 55,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 18,85</t>
+          <t>-12,47; 20,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 5,51</t>
+          <t>-24,38; 4,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 11,84</t>
+          <t>-10,43; 22,33</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>1,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,3</t>
+          <t>-0,33; 7,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,86</t>
+          <t>-3,05; 5,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,25</t>
+          <t>-0,45; 8,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,17</t>
+          <t>-4,17; 3,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 7,55</t>
+          <t>-0,49; 7,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,33; -0,34</t>
+          <t>-4,89; 2,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,3</t>
+          <t>-0,93; 4,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,11</t>
+          <t>-0,72; 5,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,37</t>
+          <t>-1,35; 4,24</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-31,89%</t>
+          <t>-7,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,4%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 58,91</t>
+          <t>-2,72; 61,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 39,74</t>
+          <t>-17,89; 41,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 65,09</t>
+          <t>-2,75; 69,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 25,74</t>
+          <t>-25,85; 27,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 60,7</t>
+          <t>-2,72; 60,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,46; -2,86</t>
+          <t>-29,32; 20,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 33,25</t>
+          <t>-6,13; 32,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 38,12</t>
+          <t>-4,43; 38,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 17,4</t>
+          <t>-8,96; 31,95</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,51</t>
+          <t>-3,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-2,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 7,31</t>
+          <t>0,87; 7,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,56</t>
+          <t>-1,91; 4,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,43</t>
+          <t>-3,67; 3,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,74</t>
+          <t>-3,41; 2,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,37</t>
+          <t>-1,34; 5,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,66</t>
+          <t>-6,63; -1,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,77</t>
+          <t>-0,61; 4,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,61</t>
+          <t>-0,69; 3,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -0,61</t>
+          <t>-4,38; -0,07</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,1%</t>
+          <t>-3,48%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-32,69%</t>
+          <t>-27,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,53%</t>
+          <t>-15,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 52,45</t>
+          <t>5,09; 53,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 33,95</t>
+          <t>-11,89; 33,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 18,27</t>
+          <t>-22,56; 22,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 21,95</t>
+          <t>-22,42; 22,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 34,83</t>
+          <t>-8,39; 42,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -13,43</t>
+          <t>-43,72; -8,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 28,94</t>
+          <t>-4,12; 30,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 27,53</t>
+          <t>-4,49; 26,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,84; -4,78</t>
+          <t>-28,41; -0,51</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>1,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,55</t>
+          <t>0,05; 3,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,51</t>
+          <t>-4,09; -0,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,04</t>
+          <t>-0,76; 3,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,69</t>
+          <t>-0,43; 2,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,7</t>
+          <t>-0,56; 2,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,64</t>
+          <t>-0,43; 2,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,69</t>
+          <t>0,19; 2,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,71</t>
+          <t>-1,72; 0,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,28</t>
+          <t>-0,18; 2,35</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-1,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,95%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,36; 23,88</t>
+          <t>0,29; 24,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,68; -3,25</t>
+          <t>-24,28; -3,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 13,27</t>
+          <t>-4,45; 21,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 22,97</t>
+          <t>-3,31; 21,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 22,52</t>
+          <t>-4,13; 22,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 14,04</t>
+          <t>-3,14; 21,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,17; 20,01</t>
+          <t>1,27; 19,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 5,31</t>
+          <t>-11,87; 4,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 9,34</t>
+          <t>-1,32; 17,15</t>
         </is>
       </c>
     </row>
